--- a/Output-Data/StudyChair.xlsx
+++ b/Output-Data/StudyChair.xlsx
@@ -26,7 +26,7 @@
     <t>Venturi Study Chair in Aqua Colour | ₹8,999</t>
   </si>
   <si>
-    <t>Cohen Study Chair in Black Colour | ₹7,999</t>
+    <t>Edmund Study Chair in Black Colour | ₹8,999</t>
   </si>
 </sst>
 </file>
